--- a/artfynd/A 32981-2024 artfynd.xlsx
+++ b/artfynd/A 32981-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>73982299</v>
       </c>
       <c r="B2" t="n">
-        <v>104838</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107283</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480908.6918679099</v>
+        <v>480909</v>
       </c>
       <c r="R2" t="n">
-        <v>6391910.895063105</v>
+        <v>6391911</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1980-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1988-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -804,12 +789,7 @@
         <v>73982667</v>
       </c>
       <c r="B3" t="n">
-        <v>106707</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109171</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480908.6918679099</v>
+        <v>480909</v>
       </c>
       <c r="R3" t="n">
-        <v>6391910.895063105</v>
+        <v>6391911</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -874,19 +854,9 @@
           <t>1980-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1988-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -930,12 +900,7 @@
         <v>74208718</v>
       </c>
       <c r="B4" t="n">
-        <v>96926</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99215</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -967,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480908.6918679099</v>
+        <v>480909</v>
       </c>
       <c r="R4" t="n">
-        <v>6391910.895063105</v>
+        <v>6391911</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1000,19 +965,9 @@
           <t>1980-01-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1988-12-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">

--- a/artfynd/A 32981-2024 artfynd.xlsx
+++ b/artfynd/A 32981-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982299</v>
       </c>
       <c r="B2" t="n">
-        <v>107283</v>
+        <v>107292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>73982667</v>
       </c>
       <c r="B3" t="n">
-        <v>109171</v>
+        <v>109180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74208718</v>
       </c>
       <c r="B4" t="n">
-        <v>99215</v>
+        <v>99220</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32981-2024 artfynd.xlsx
+++ b/artfynd/A 32981-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982299</v>
       </c>
       <c r="B2" t="n">
-        <v>107292</v>
+        <v>107297</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>73982667</v>
       </c>
       <c r="B3" t="n">
-        <v>109180</v>
+        <v>109185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74208718</v>
       </c>
       <c r="B4" t="n">
-        <v>99220</v>
+        <v>99221</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32981-2024 artfynd.xlsx
+++ b/artfynd/A 32981-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982299</v>
       </c>
       <c r="B2" t="n">
-        <v>107297</v>
+        <v>107325</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>73982667</v>
       </c>
       <c r="B3" t="n">
-        <v>109185</v>
+        <v>109213</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74208718</v>
       </c>
       <c r="B4" t="n">
-        <v>99221</v>
+        <v>99248</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32981-2024 artfynd.xlsx
+++ b/artfynd/A 32981-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982299</v>
       </c>
       <c r="B2" t="n">
-        <v>107325</v>
+        <v>107331</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>73982667</v>
       </c>
       <c r="B3" t="n">
-        <v>109213</v>
+        <v>109219</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74208718</v>
       </c>
       <c r="B4" t="n">
-        <v>99248</v>
+        <v>99254</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32981-2024 artfynd.xlsx
+++ b/artfynd/A 32981-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982299</v>
       </c>
       <c r="B2" t="n">
-        <v>107331</v>
+        <v>107338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>73982667</v>
       </c>
       <c r="B3" t="n">
-        <v>109219</v>
+        <v>109226</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74208718</v>
       </c>
       <c r="B4" t="n">
-        <v>99254</v>
+        <v>99261</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32981-2024 artfynd.xlsx
+++ b/artfynd/A 32981-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982299</v>
       </c>
       <c r="B2" t="n">
-        <v>107338</v>
+        <v>107342</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>73982667</v>
       </c>
       <c r="B3" t="n">
-        <v>109226</v>
+        <v>109230</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74208718</v>
       </c>
       <c r="B4" t="n">
-        <v>99261</v>
+        <v>99265</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32981-2024 artfynd.xlsx
+++ b/artfynd/A 32981-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982299</v>
       </c>
       <c r="B2" t="n">
-        <v>107342</v>
+        <v>107350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>73982667</v>
       </c>
       <c r="B3" t="n">
-        <v>109230</v>
+        <v>109238</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74208718</v>
       </c>
       <c r="B4" t="n">
-        <v>99265</v>
+        <v>99272</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32981-2024 artfynd.xlsx
+++ b/artfynd/A 32981-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982299</v>
       </c>
       <c r="B2" t="n">
-        <v>107353</v>
+        <v>107358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>73982667</v>
       </c>
       <c r="B3" t="n">
-        <v>109241</v>
+        <v>109246</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74208718</v>
       </c>
       <c r="B4" t="n">
-        <v>99275</v>
+        <v>99280</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32981-2024 artfynd.xlsx
+++ b/artfynd/A 32981-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982299</v>
       </c>
       <c r="B2" t="n">
-        <v>107358</v>
+        <v>107366</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>73982667</v>
       </c>
       <c r="B3" t="n">
-        <v>109246</v>
+        <v>109254</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74208718</v>
       </c>
       <c r="B4" t="n">
-        <v>99280</v>
+        <v>99288</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32981-2024 artfynd.xlsx
+++ b/artfynd/A 32981-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73982299</v>
       </c>
       <c r="B2" t="n">
-        <v>107366</v>
+        <v>107376</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>73982667</v>
       </c>
       <c r="B3" t="n">
-        <v>109254</v>
+        <v>109264</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74208718</v>
       </c>
       <c r="B4" t="n">
-        <v>99288</v>
+        <v>99298</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32981-2024 artfynd.xlsx
+++ b/artfynd/A 32981-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>73982299</v>
       </c>
       <c r="B2" t="n">
-        <v>107376</v>
+        <v>107907</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>73982667</v>
       </c>
       <c r="B3" t="n">
-        <v>109264</v>
+        <v>109814</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>74208718</v>
+        <v>75338935</v>
       </c>
       <c r="B4" t="n">
-        <v>99298</v>
+        <v>109815</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,34 +908,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222295</v>
+        <v>220204</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vårstarr</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carex caryophyllea</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Latourr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>L9 Sticket 500 m O, Sm</t>
+          <t>Sticket 500 m O (2), Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480909</v>
+        <v>480926</v>
       </c>
       <c r="R4" t="n">
-        <v>6391911</v>
+        <v>6391891</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -960,9 +964,14 @@
           <t>Nässjö</t>
         </is>
       </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Arkiv-F-Näs-0189</t>
+        </is>
+      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1980-01-01</t>
+          <t>1988-12-31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -972,7 +981,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6E8g 4328. SOM: Carex caryophyllea. LEG: Einar Mörk, Torsten Karlsson</t>
+          <t>KOO: 6E8g 4328.  LEG: Einar Mörk, Torsten Karlsson</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,12 +990,13 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Grusås</t>
+          <t>Äng</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1002,21 +1012,16 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>Smålands flora (1978-2007)</t>
+          <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>75338935</v>
+        <v>74782778</v>
       </c>
       <c r="B5" t="n">
-        <v>106707</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102559</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,16 +1029,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220204</v>
+        <v>222133</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Polygala vulgaris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1042,20 +1047,16 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sticket 500 m O (2), Sm</t>
+          <t>L9 Sticket 500 m O, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480926.2823786732</v>
+        <v>480909</v>
       </c>
       <c r="R5" t="n">
-        <v>6391891.022415667</v>
+        <v>6391911</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1080,34 +1081,19 @@
           <t>Nässjö</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>F-Näs-0557</t>
-        </is>
-      </c>
       <c r="Y5" t="inlineStr">
         <is>
+          <t>1980-01-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
           <t>1988-12-31</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>1988-12-31</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>KOO: 6E8g 4328.  LEG: Einar Mörk, Torsten Karlsson</t>
+          <t>Smålands flora 2007: KOO: 6E8g 4328. SOM: Polygala vulgaris. LEG: Einar Mörk, Torsten Karlsson</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,13 +1102,12 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Äng</t>
+          <t>Hage</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1138,7 +1123,118 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>74208718</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99754</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222295</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vårstarr</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Carex caryophyllea</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Latourr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>L9 Sticket 500 m O, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>480909</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6391911</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nässjö</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Nässjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>1980-01-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>1988-12-31</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 6E8g 4328. SOM: Carex caryophyllea. LEG: Einar Mörk, Torsten Karlsson</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Grusås</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 32981-2024 artfynd.xlsx
+++ b/artfynd/A 32981-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73982299</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
       <c r="AY3" t="inlineStr">
         <is>
           <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73982667</t>
         </is>
       </c>
     </row>
@@ -1015,6 +1030,11 @@
           <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75338935</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1126,6 +1146,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74782778</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1237,8 +1262,20 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74208718</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>